--- a/Advance Excel/VLOOKUP in Excel.xlsx
+++ b/Advance Excel/VLOOKUP in Excel.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Naik Balkrushna Anil\OneDrive\Attachments\Desktop\Full Stack Development\Exploring Data Science Field\Microsoft Excel\Advance Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Naik Balkrushna Anil\OneDrive\Attachments\Desktop\Full Stack Development\Data Analytics\Microsoft Excel\Advance Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63BFADFF-36E2-4AC3-A22E-1278D54FFA70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF3762B-1B85-4A82-88A1-8831A482C867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="115">
   <si>
     <t>Student ID</t>
   </si>
@@ -367,13 +367,16 @@
   </si>
   <si>
     <t>Performing Vlookup Operations in Table</t>
+  </si>
+  <si>
+    <t>Indexing start from 1 in Excel</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -398,8 +401,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -418,8 +429,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -427,11 +444,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -442,10 +496,25 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -454,25 +523,7 @@
   </cellStyles>
   <dxfs count="12">
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -504,13 +555,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -557,6 +602,31 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -571,30 +641,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E6D0DFC0-105C-46E2-8F3A-83EE82159786}" name="Table1" displayName="Table1" ref="A1:D101" totalsRowShown="0" headerRowDxfId="6" dataDxfId="7">
-  <autoFilter ref="A1:D101" xr:uid="{E6D0DFC0-105C-46E2-8F3A-83EE82159786}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E6D0DFC0-105C-46E2-8F3A-83EE82159786}" name="Table1" displayName="Table1" ref="A1:D101" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{919624EF-E248-4C67-9CA9-F70931263B77}" name="Student ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{0839435B-4A23-48D7-BB09-96B2C4C6E505}" name="Name" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{4F787FC1-424E-4912-BAF5-2FBB986B4B3C}" name="Course" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{A09B8775-9354-4C0B-98D0-622F4B80E71C}" name="Marks" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{919624EF-E248-4C67-9CA9-F70931263B77}" name="Student ID" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{0839435B-4A23-48D7-BB09-96B2C4C6E505}" name="Name" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{4F787FC1-424E-4912-BAF5-2FBB986B4B3C}" name="Course" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{A09B8775-9354-4C0B-98D0-622F4B80E71C}" name="Marks" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{782DC361-1440-4809-9828-A61D350C0061}" name="Table2" displayName="Table2" ref="G5:J21" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
-  <autoFilter ref="G5:J21" xr:uid="{782DC361-1440-4809-9828-A61D350C0061}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{782DC361-1440-4809-9828-A61D350C0061}" name="Table2" displayName="Table2" ref="G5:J21" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{5CA704CE-E846-45A1-998E-700290E87BD4}" name="Enter ID" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{CCF782D3-2D23-45D1-9E44-D1C58BEA0E50}" name="Result Name" dataDxfId="4">
-      <calculatedColumnFormula>VLOOKUP(G6,$A$1:$D$101,2,)</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{5CA704CE-E846-45A1-998E-700290E87BD4}" name="Enter ID" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{CCF782D3-2D23-45D1-9E44-D1C58BEA0E50}" name="Result Name" dataDxfId="0">
+      <calculatedColumnFormula>VLOOKUP(G6,Table1[#All],2,)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B6665467-E601-43D5-AF91-55F011711DBA}" name="Result Course" dataDxfId="3">
+    <tableColumn id="3" xr3:uid="{B6665467-E601-43D5-AF91-55F011711DBA}" name="Result Course" dataDxfId="2">
       <calculatedColumnFormula>VLOOKUP(G6,$A$1:$D$101,3,)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EF0EE963-DA0C-48D8-825F-D9AC9309C325}" name="Result Marks" dataDxfId="2">
+    <tableColumn id="4" xr3:uid="{EF0EE963-DA0C-48D8-825F-D9AC9309C325}" name="Result Marks" dataDxfId="1">
       <calculatedColumnFormula>VLOOKUP(G6,A1:D101,4,)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -865,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="27.6" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="8" max="8" width="13.44140625" customWidth="1"/>
@@ -873,21 +941,21 @@
     <col min="10" max="10" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>101</v>
       </c>
@@ -901,7 +969,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>102</v>
       </c>
@@ -914,14 +982,18 @@
       <c r="D3" s="3">
         <v>63</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-    </row>
-    <row r="4" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="L3" s="10"/>
+    </row>
+    <row r="4" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>103</v>
       </c>
@@ -935,7 +1007,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>104</v>
       </c>
@@ -960,8 +1032,20 @@
       <c r="J5" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>105</v>
       </c>
@@ -978,7 +1062,7 @@
         <v>103</v>
       </c>
       <c r="H6" s="2" t="str">
-        <f>VLOOKUP(G6,$A$1:$D$101,2,)</f>
+        <f>VLOOKUP(G6,Table1[#All],2,)</f>
         <v>Rahul</v>
       </c>
       <c r="I6" s="2" t="str">
@@ -989,8 +1073,23 @@
         <f>VLOOKUP(G6,A1:D101,4,)</f>
         <v>66</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M6" s="9">
+        <v>114</v>
+      </c>
+      <c r="N6" t="str">
+        <f>VLOOKUP(M6,Table1[#All],2,)</f>
+        <v>Kavita</v>
+      </c>
+      <c r="O6" t="str">
+        <f>VLOOKUP(M6,Table1[#All],3,)</f>
+        <v>Data Analytics</v>
+      </c>
+      <c r="P6">
+        <f>VLOOKUP(M6,Table1[#All],4,)</f>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>106</v>
       </c>
@@ -1007,19 +1106,34 @@
         <v>104</v>
       </c>
       <c r="H7" s="2" t="str">
-        <f t="shared" ref="H7:H21" si="0">VLOOKUP(G7,$A$1:$D$101,2,)</f>
+        <f>VLOOKUP(G7,Table1[#All],2,)</f>
         <v>Sneha</v>
       </c>
       <c r="I7" s="2" t="str">
-        <f t="shared" ref="I7:I21" si="1">VLOOKUP(G7,$A$1:$D$101,3,)</f>
+        <f t="shared" ref="I7:I21" si="0">VLOOKUP(G7,$A$1:$D$101,3,)</f>
         <v>Data Analytics</v>
       </c>
       <c r="J7" s="2">
-        <f t="shared" ref="J7:J21" si="2">VLOOKUP(G7,A2:D102,4,)</f>
+        <f t="shared" ref="J7:J21" si="1">VLOOKUP(G7,A2:D102,4,)</f>
         <v>69</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M7" s="9">
+        <v>115</v>
+      </c>
+      <c r="N7" t="str">
+        <f>VLOOKUP(M7,Table1[#All],2,)</f>
+        <v>Nikhil</v>
+      </c>
+      <c r="O7" t="str">
+        <f>VLOOKUP(M7,Table1[#All],3,)</f>
+        <v>Power BI</v>
+      </c>
+      <c r="P7">
+        <f>VLOOKUP(M7,Table1[#All],4,)</f>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>107</v>
       </c>
@@ -1036,19 +1150,34 @@
         <v>105</v>
       </c>
       <c r="H8" s="2" t="str">
+        <f>VLOOKUP(G8,Table1[#All],2,)</f>
+        <v>Kiran</v>
+      </c>
+      <c r="I8" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Kiran</v>
-      </c>
-      <c r="I8" s="2" t="str">
+        <v>Power BI</v>
+      </c>
+      <c r="J8" s="2">
         <f t="shared" si="1"/>
-        <v>Power BI</v>
-      </c>
-      <c r="J8" s="2">
-        <f t="shared" si="2"/>
         <v>72</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M8" s="9">
+        <v>116</v>
+      </c>
+      <c r="N8" t="str">
+        <f>VLOOKUP(M8,Table1[#All],2,)</f>
+        <v>Riya</v>
+      </c>
+      <c r="O8" t="str">
+        <f>VLOOKUP(M8,Table1[#All],3,)</f>
+        <v>Python</v>
+      </c>
+      <c r="P8">
+        <f>VLOOKUP(M8,Table1[#All],4,)</f>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>108</v>
       </c>
@@ -1065,19 +1194,34 @@
         <v>106</v>
       </c>
       <c r="H9" s="2" t="str">
+        <f>VLOOKUP(G9,Table1[#All],2,)</f>
+        <v>Anjali</v>
+      </c>
+      <c r="I9" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Anjali</v>
-      </c>
-      <c r="I9" s="2" t="str">
+        <v>Python</v>
+      </c>
+      <c r="J9" s="2">
         <f t="shared" si="1"/>
-        <v>Python</v>
-      </c>
-      <c r="J9" s="2">
-        <f t="shared" si="2"/>
         <v>75</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M9" s="9">
+        <v>117</v>
+      </c>
+      <c r="N9" t="str">
+        <f>VLOOKUP(M9,Table1[#All],2,)</f>
+        <v>Manoj</v>
+      </c>
+      <c r="O9" t="str">
+        <f>VLOOKUP(M9,Table1[#All],3,)</f>
+        <v>Excel</v>
+      </c>
+      <c r="P9">
+        <f>VLOOKUP(M9,Table1[#All],4,)</f>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>109</v>
       </c>
@@ -1094,19 +1238,34 @@
         <v>107</v>
       </c>
       <c r="H10" s="2" t="str">
+        <f>VLOOKUP(G10,Table1[#All],2,)</f>
+        <v>Rohit</v>
+      </c>
+      <c r="I10" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Rohit</v>
-      </c>
-      <c r="I10" s="2" t="str">
+        <v>Excel</v>
+      </c>
+      <c r="J10" s="2">
         <f t="shared" si="1"/>
-        <v>Excel</v>
-      </c>
-      <c r="J10" s="2">
-        <f t="shared" si="2"/>
         <v>78</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M10" s="9">
+        <v>118</v>
+      </c>
+      <c r="N10" t="str">
+        <f>VLOOKUP(M10,Table1[#All],2,)</f>
+        <v>Swati</v>
+      </c>
+      <c r="O10" t="str">
+        <f>VLOOKUP(M10,Table1[#All],3,)</f>
+        <v>SQL</v>
+      </c>
+      <c r="P10">
+        <f>VLOOKUP(M10,Table1[#All],4,)</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>110</v>
       </c>
@@ -1123,19 +1282,34 @@
         <v>108</v>
       </c>
       <c r="H11" s="2" t="str">
+        <f>VLOOKUP(G11,Table1[#All],2,)</f>
+        <v>Neha</v>
+      </c>
+      <c r="I11" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Neha</v>
-      </c>
-      <c r="I11" s="2" t="str">
+        <v>SQL</v>
+      </c>
+      <c r="J11" s="2">
         <f t="shared" si="1"/>
-        <v>SQL</v>
-      </c>
-      <c r="J11" s="2">
-        <f t="shared" si="2"/>
         <v>81</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M11" s="9">
+        <v>119</v>
+      </c>
+      <c r="N11" t="str">
+        <f>VLOOKUP(M11,Table1[#All],2,)</f>
+        <v>Ajay</v>
+      </c>
+      <c r="O11" t="str">
+        <f>VLOOKUP(M11,Table1[#All],3,)</f>
+        <v>Data Analytics</v>
+      </c>
+      <c r="P11">
+        <f>VLOOKUP(M11,Table1[#All],4,)</f>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>111</v>
       </c>
@@ -1152,19 +1326,34 @@
         <v>109</v>
       </c>
       <c r="H12" s="2" t="str">
+        <f>VLOOKUP(G12,Table1[#All],2,)</f>
+        <v>Vikram</v>
+      </c>
+      <c r="I12" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Vikram</v>
-      </c>
-      <c r="I12" s="2" t="str">
+        <v>Data Analytics</v>
+      </c>
+      <c r="J12" s="2">
         <f t="shared" si="1"/>
-        <v>Data Analytics</v>
-      </c>
-      <c r="J12" s="2">
-        <f t="shared" si="2"/>
         <v>84</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M12" s="9">
+        <v>120</v>
+      </c>
+      <c r="N12" t="str">
+        <f>VLOOKUP(M12,Table1[#All],2,)</f>
+        <v>Komal</v>
+      </c>
+      <c r="O12" t="str">
+        <f>VLOOKUP(M12,Table1[#All],3,)</f>
+        <v>Power BI</v>
+      </c>
+      <c r="P12">
+        <f>VLOOKUP(M12,Table1[#All],4,)</f>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>112</v>
       </c>
@@ -1181,19 +1370,34 @@
         <v>110</v>
       </c>
       <c r="H13" s="2" t="str">
+        <f>VLOOKUP(G13,Table1[#All],2,)</f>
+        <v>Pooja</v>
+      </c>
+      <c r="I13" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Pooja</v>
-      </c>
-      <c r="I13" s="2" t="str">
+        <v>Power BI</v>
+      </c>
+      <c r="J13" s="2">
         <f t="shared" si="1"/>
-        <v>Power BI</v>
-      </c>
-      <c r="J13" s="2">
-        <f t="shared" si="2"/>
         <v>87</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M13" s="9">
+        <v>121</v>
+      </c>
+      <c r="N13" t="str">
+        <f>VLOOKUP(M13,Table1[#All],2,)</f>
+        <v>Deepak</v>
+      </c>
+      <c r="O13" t="str">
+        <f>VLOOKUP(M13,Table1[#All],3,)</f>
+        <v>Python</v>
+      </c>
+      <c r="P13">
+        <f>VLOOKUP(M13,Table1[#All],4,)</f>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>113</v>
       </c>
@@ -1210,19 +1414,34 @@
         <v>111</v>
       </c>
       <c r="H14" s="2" t="str">
+        <f>VLOOKUP(G14,Table1[#All],2,)</f>
+        <v>Arjun</v>
+      </c>
+      <c r="I14" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Arjun</v>
-      </c>
-      <c r="I14" s="2" t="str">
+        <v>Python</v>
+      </c>
+      <c r="J14" s="2">
         <f t="shared" si="1"/>
-        <v>Python</v>
-      </c>
-      <c r="J14" s="2">
-        <f t="shared" si="2"/>
         <v>90</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M14" s="9">
+        <v>122</v>
+      </c>
+      <c r="N14" t="str">
+        <f>VLOOKUP(M14,Table1[#All],2,)</f>
+        <v>Sonali</v>
+      </c>
+      <c r="O14" t="str">
+        <f>VLOOKUP(M14,Table1[#All],3,)</f>
+        <v>Excel</v>
+      </c>
+      <c r="P14">
+        <f>VLOOKUP(M14,Table1[#All],4,)</f>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>114</v>
       </c>
@@ -1239,19 +1458,34 @@
         <v>112</v>
       </c>
       <c r="H15" s="2" t="str">
+        <f>VLOOKUP(G15,Table1[#All],2,)</f>
+        <v>Meena</v>
+      </c>
+      <c r="I15" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Meena</v>
-      </c>
-      <c r="I15" s="2" t="str">
+        <v>Excel</v>
+      </c>
+      <c r="J15" s="2">
         <f t="shared" si="1"/>
-        <v>Excel</v>
-      </c>
-      <c r="J15" s="2">
-        <f t="shared" si="2"/>
         <v>93</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M15" s="9">
+        <v>123</v>
+      </c>
+      <c r="N15" t="str">
+        <f>VLOOKUP(M15,Table1[#All],2,)</f>
+        <v>Yash</v>
+      </c>
+      <c r="O15" t="str">
+        <f>VLOOKUP(M15,Table1[#All],3,)</f>
+        <v>SQL</v>
+      </c>
+      <c r="P15">
+        <f>VLOOKUP(M15,Table1[#All],4,)</f>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>115</v>
       </c>
@@ -1268,19 +1502,34 @@
         <v>113</v>
       </c>
       <c r="H16" s="2" t="str">
+        <f>VLOOKUP(G16,Table1[#All],2,)</f>
+        <v>Sagar</v>
+      </c>
+      <c r="I16" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Sagar</v>
-      </c>
-      <c r="I16" s="2" t="str">
+        <v>SQL</v>
+      </c>
+      <c r="J16" s="2">
         <f t="shared" si="1"/>
-        <v>SQL</v>
-      </c>
-      <c r="J16" s="2">
-        <f t="shared" si="2"/>
         <v>96</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M16" s="9">
+        <v>124</v>
+      </c>
+      <c r="N16" t="str">
+        <f>VLOOKUP(M16,Table1[#All],2,)</f>
+        <v>Aarti</v>
+      </c>
+      <c r="O16" t="str">
+        <f>VLOOKUP(M16,Table1[#All],3,)</f>
+        <v>Data Analytics</v>
+      </c>
+      <c r="P16">
+        <f>VLOOKUP(M16,Table1[#All],4,)</f>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>116</v>
       </c>
@@ -1297,19 +1546,34 @@
         <v>114</v>
       </c>
       <c r="H17" s="2" t="str">
+        <f>VLOOKUP(G17,Table1[#All],2,)</f>
+        <v>Kavita</v>
+      </c>
+      <c r="I17" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Kavita</v>
-      </c>
-      <c r="I17" s="2" t="str">
+        <v>Data Analytics</v>
+      </c>
+      <c r="J17" s="2">
         <f t="shared" si="1"/>
-        <v>Data Analytics</v>
-      </c>
-      <c r="J17" s="2">
-        <f t="shared" si="2"/>
         <v>99</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M17" s="9">
+        <v>125</v>
+      </c>
+      <c r="N17" t="str">
+        <f>VLOOKUP(M17,Table1[#All],2,)</f>
+        <v>Sameer</v>
+      </c>
+      <c r="O17" t="str">
+        <f>VLOOKUP(M17,Table1[#All],3,)</f>
+        <v>Power BI</v>
+      </c>
+      <c r="P17">
+        <f>VLOOKUP(M17,Table1[#All],4,)</f>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>117</v>
       </c>
@@ -1326,19 +1590,34 @@
         <v>115</v>
       </c>
       <c r="H18" s="2" t="str">
+        <f>VLOOKUP(G18,Table1[#All],2,)</f>
+        <v>Nikhil</v>
+      </c>
+      <c r="I18" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Nikhil</v>
-      </c>
-      <c r="I18" s="2" t="str">
+        <v>Power BI</v>
+      </c>
+      <c r="J18" s="2">
         <f t="shared" si="1"/>
-        <v>Power BI</v>
-      </c>
-      <c r="J18" s="2">
-        <f t="shared" si="2"/>
         <v>61</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M18" s="9">
+        <v>126</v>
+      </c>
+      <c r="N18" t="str">
+        <f>VLOOKUP(M18,Table1[#All],2,)</f>
+        <v>Nisha</v>
+      </c>
+      <c r="O18" t="str">
+        <f>VLOOKUP(M18,Table1[#All],3,)</f>
+        <v>Python</v>
+      </c>
+      <c r="P18">
+        <f>VLOOKUP(M18,Table1[#All],4,)</f>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>118</v>
       </c>
@@ -1355,19 +1634,34 @@
         <v>116</v>
       </c>
       <c r="H19" s="2" t="str">
+        <f>VLOOKUP(G19,Table1[#All],2,)</f>
+        <v>Riya</v>
+      </c>
+      <c r="I19" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Riya</v>
-      </c>
-      <c r="I19" s="2" t="str">
+        <v>Python</v>
+      </c>
+      <c r="J19" s="2">
         <f t="shared" si="1"/>
-        <v>Python</v>
-      </c>
-      <c r="J19" s="2">
-        <f t="shared" si="2"/>
         <v>64</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M19" s="9">
+        <v>127</v>
+      </c>
+      <c r="N19" t="str">
+        <f>VLOOKUP(M19,Table1[#All],2,)</f>
+        <v>Tushar</v>
+      </c>
+      <c r="O19" t="str">
+        <f>VLOOKUP(M19,Table1[#All],3,)</f>
+        <v>Excel</v>
+      </c>
+      <c r="P19">
+        <f>VLOOKUP(M19,Table1[#All],4,)</f>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>119</v>
       </c>
@@ -1384,19 +1678,34 @@
         <v>117</v>
       </c>
       <c r="H20" s="2" t="str">
+        <f>VLOOKUP(G20,Table1[#All],2,)</f>
+        <v>Manoj</v>
+      </c>
+      <c r="I20" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Manoj</v>
-      </c>
-      <c r="I20" s="2" t="str">
+        <v>Excel</v>
+      </c>
+      <c r="J20" s="2">
         <f t="shared" si="1"/>
-        <v>Excel</v>
-      </c>
-      <c r="J20" s="2">
-        <f t="shared" si="2"/>
         <v>67</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M20" s="9">
+        <v>128</v>
+      </c>
+      <c r="N20" t="str">
+        <f>VLOOKUP(M20,Table1[#All],2,)</f>
+        <v>Rekha</v>
+      </c>
+      <c r="O20" t="str">
+        <f>VLOOKUP(M20,Table1[#All],3,)</f>
+        <v>SQL</v>
+      </c>
+      <c r="P20">
+        <f>VLOOKUP(M20,Table1[#All],4,)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>120</v>
       </c>
@@ -1413,19 +1722,34 @@
         <v>118</v>
       </c>
       <c r="H21" s="2" t="str">
+        <f>VLOOKUP(G21,Table1[#All],2,)</f>
+        <v>Swati</v>
+      </c>
+      <c r="I21" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Swati</v>
-      </c>
-      <c r="I21" s="2" t="str">
+        <v>SQL</v>
+      </c>
+      <c r="J21" s="2">
         <f t="shared" si="1"/>
-        <v>SQL</v>
-      </c>
-      <c r="J21" s="2">
-        <f t="shared" si="2"/>
         <v>70</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M21" s="9">
+        <v>129</v>
+      </c>
+      <c r="N21" t="str">
+        <f>VLOOKUP(M21,Table1[#All],2,)</f>
+        <v>Akash</v>
+      </c>
+      <c r="O21" t="str">
+        <f>VLOOKUP(M21,Table1[#All],3,)</f>
+        <v>Data Analytics</v>
+      </c>
+      <c r="P21">
+        <f>VLOOKUP(M21,Table1[#All],4,)</f>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>121</v>
       </c>
@@ -1438,8 +1762,23 @@
       <c r="D22" s="3">
         <v>79</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M22" s="9">
+        <v>130</v>
+      </c>
+      <c r="N22" t="str">
+        <f>VLOOKUP(M22,Table1[#All],2,)</f>
+        <v>Seema</v>
+      </c>
+      <c r="O22" t="str">
+        <f>VLOOKUP(M22,Table1[#All],3,)</f>
+        <v>Power BI</v>
+      </c>
+      <c r="P22">
+        <f>VLOOKUP(M22,Table1[#All],4,)</f>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>122</v>
       </c>
@@ -1452,8 +1791,23 @@
       <c r="D23" s="3">
         <v>82</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M23" s="9">
+        <v>131</v>
+      </c>
+      <c r="N23" t="str">
+        <f>VLOOKUP(M23,Table1[#All],2,)</f>
+        <v>Varun</v>
+      </c>
+      <c r="O23" t="str">
+        <f>VLOOKUP(M23,Table1[#All],3,)</f>
+        <v>Python</v>
+      </c>
+      <c r="P23">
+        <f>VLOOKUP(M23,Table1[#All],4,)</f>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>123</v>
       </c>
@@ -1466,8 +1820,23 @@
       <c r="D24" s="3">
         <v>85</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M24" s="9">
+        <v>132</v>
+      </c>
+      <c r="N24" t="str">
+        <f>VLOOKUP(M24,Table1[#All],2,)</f>
+        <v>Jyoti</v>
+      </c>
+      <c r="O24" t="str">
+        <f>VLOOKUP(M24,Table1[#All],3,)</f>
+        <v>Excel</v>
+      </c>
+      <c r="P24">
+        <f>VLOOKUP(M24,Table1[#All],4,)</f>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>124</v>
       </c>
@@ -1480,8 +1849,23 @@
       <c r="D25" s="3">
         <v>88</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M25" s="9">
+        <v>133</v>
+      </c>
+      <c r="N25" t="str">
+        <f>VLOOKUP(M25,Table1[#All],2,)</f>
+        <v>Gaurav</v>
+      </c>
+      <c r="O25" t="str">
+        <f>VLOOKUP(M25,Table1[#All],3,)</f>
+        <v>SQL</v>
+      </c>
+      <c r="P25">
+        <f>VLOOKUP(M25,Table1[#All],4,)</f>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>125</v>
       </c>
@@ -1494,8 +1878,23 @@
       <c r="D26" s="3">
         <v>91</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M26" s="9">
+        <v>134</v>
+      </c>
+      <c r="N26" t="str">
+        <f>VLOOKUP(M26,Table1[#All],2,)</f>
+        <v>Pallavi</v>
+      </c>
+      <c r="O26" t="str">
+        <f>VLOOKUP(M26,Table1[#All],3,)</f>
+        <v>Data Analytics</v>
+      </c>
+      <c r="P26">
+        <f>VLOOKUP(M26,Table1[#All],4,)</f>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>126</v>
       </c>
@@ -1508,8 +1907,23 @@
       <c r="D27" s="3">
         <v>94</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M27" s="9">
+        <v>135</v>
+      </c>
+      <c r="N27" t="str">
+        <f>VLOOKUP(M27,Table1[#All],2,)</f>
+        <v>Ramesh</v>
+      </c>
+      <c r="O27" t="str">
+        <f>VLOOKUP(M27,Table1[#All],3,)</f>
+        <v>Power BI</v>
+      </c>
+      <c r="P27">
+        <f>VLOOKUP(M27,Table1[#All],4,)</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>127</v>
       </c>
@@ -1522,8 +1936,23 @@
       <c r="D28" s="3">
         <v>97</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M28" s="9">
+        <v>136</v>
+      </c>
+      <c r="N28" t="str">
+        <f>VLOOKUP(M28,Table1[#All],2,)</f>
+        <v>Sunita</v>
+      </c>
+      <c r="O28" t="str">
+        <f>VLOOKUP(M28,Table1[#All],3,)</f>
+        <v>Python</v>
+      </c>
+      <c r="P28">
+        <f>VLOOKUP(M28,Table1[#All],4,)</f>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>128</v>
       </c>
@@ -1536,8 +1965,23 @@
       <c r="D29" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M29" s="9">
+        <v>137</v>
+      </c>
+      <c r="N29" t="str">
+        <f>VLOOKUP(M29,Table1[#All],2,)</f>
+        <v>Mahesh</v>
+      </c>
+      <c r="O29" t="str">
+        <f>VLOOKUP(M29,Table1[#All],3,)</f>
+        <v>Excel</v>
+      </c>
+      <c r="P29">
+        <f>VLOOKUP(M29,Table1[#All],4,)</f>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>129</v>
       </c>
@@ -1550,8 +1994,23 @@
       <c r="D30" s="3">
         <v>62</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M30" s="9">
+        <v>138</v>
+      </c>
+      <c r="N30" t="str">
+        <f>VLOOKUP(M30,Table1[#All],2,)</f>
+        <v>Bhavna</v>
+      </c>
+      <c r="O30" t="str">
+        <f>VLOOKUP(M30,Table1[#All],3,)</f>
+        <v>SQL</v>
+      </c>
+      <c r="P30">
+        <f>VLOOKUP(M30,Table1[#All],4,)</f>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>130</v>
       </c>
@@ -1565,7 +2024,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>131</v>
       </c>
@@ -2546,8 +3005,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="G3:J3"/>
+    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
